--- a/artfynd/A 59885-2021 artfynd.xlsx
+++ b/artfynd/A 59885-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59885-2021 artfynd.xlsx
+++ b/artfynd/A 59885-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,6 +1474,127 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107140910</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90252</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vifors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609948</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6758232</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-03-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-03-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
